--- a/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
+++ b/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,12 +124,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -207,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,9 +267,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1603,23 +1594,19 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>284860800</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>60480</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1628,12 +1615,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1643,7 +1630,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8170,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -8193,7 +8180,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8490,12 +8477,12 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>- | 4710呎 (3房)
-招标单位
--
-(在售)</t>
+$28486万
+$60,480/呎
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>

--- a/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
+++ b/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +124,12 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -201,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +273,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1314,7 +1323,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1324,12 +1333,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1339,12 +1348,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1354,7 +1363,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8170,27 +8179,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -8397,12 +8406,12 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>- | 4710呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>

--- a/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
+++ b/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4710</v>
+        <v>4605</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1608,14 +1608,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
         <v>284860800</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>60480</v>
+        <v>61859</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4710</v>
+        <v>4605</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1744,14 +1744,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
         <v>285709000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>60660</v>
+        <v>62043</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -8488,10 +8488,10 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>- | 4710呎 (3房)
+          <t>- | 4605呎 (3房)
 $28486万
-$60,480/呎
-(26年-09月-04日)</t>
+$61,859/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -8528,10 +8528,10 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>- | 4710呎 (3房)
+          <t>- | 4605呎 (3房)
 $28571万
-$60,660/呎
-(26年-08月-31日)</t>
+$62,043/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>

--- a/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
+++ b/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,12 +124,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -207,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,9 +267,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1323,7 +1314,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1333,12 +1324,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1348,12 +1339,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1363,7 +1354,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8170,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -8199,7 +8190,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8397,12 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>- | 4710呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>

--- a/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
+++ b/港岛-半山区西部-天御第1期/天御第1期_销控明细表.xlsx
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4605</v>
+        <v>4710</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>284860800</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>61859</v>
+        <v>60480</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4605</v>
+        <v>4710</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>285709000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>62043</v>
+        <v>60660</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4596</v>
+        <v>4710</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>268983400</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>58526</v>
+        <v>57109</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2281</v>
+        <v>2335</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>119280000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>52293</v>
+        <v>51084</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2269</v>
+        <v>2329</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>112880000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>49749</v>
+        <v>48467</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2281</v>
+        <v>2335</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>141832000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>62180</v>
+        <v>60742</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2269</v>
+        <v>2329</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>109239000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>48144</v>
+        <v>46904</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2281</v>
+        <v>2335</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>112220000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>49198</v>
+        <v>48060</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2269</v>
+        <v>2329</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>104283800</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>45960</v>
+        <v>44776</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2281</v>
+        <v>2335</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>102138000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>44778</v>
+        <v>43742</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2269</v>
+        <v>2329</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>108200000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>47686</v>
+        <v>46458</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2281</v>
+        <v>2335</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>103370000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>45318</v>
+        <v>44270</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2269</v>
+        <v>2329</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>98000000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>43191</v>
+        <v>42078</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -8479,9 +8479,9 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>- | 4605呎 (3房)
+          <t>- | 4710呎 (3房)
 $28486万
-$61,859/呎
+$60,480/呎
 (26年-09月-17日)</t>
         </is>
       </c>
@@ -8519,9 +8519,9 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>- | 4605呎 (3房)
+          <t>- | 4710呎 (3房)
 $28571万
-$62,043/呎
+$60,660/呎
 (26年-09月-16日)</t>
         </is>
       </c>
@@ -8539,9 +8539,9 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>- | 4596呎 (3房)
+          <t>- | 4710呎 (3房)
 $26898万
-$58,526/呎
+$57,109/呎
 (26年-04月-30日)</t>
         </is>
       </c>
@@ -8560,17 +8560,17 @@
       <c r="B21" s="20" t="inlineStr"/>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>A | 2269呎 (4+房)
+          <t>A | 2329呎 (4+房)
 $11288万
-$49,749/呎
+$48,467/呎
 (25年-12月-03日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>B | 2281呎 (4+房)
+          <t>B | 2335呎 (4+房)
 $11928万
-$52,293/呎
+$51,084/呎
 (25年-11月-18日)</t>
         </is>
       </c>
@@ -8587,17 +8587,17 @@
       <c r="B22" s="20" t="inlineStr"/>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>A | 2269呎 (4+房)
+          <t>A | 2329呎 (4+房)
 $10924万
-$48,144/呎
+$46,904/呎
 (25年-11月-18日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>B | 2281呎 (4+房)
+          <t>B | 2335呎 (4+房)
 $14183万
-$62,180/呎
+$60,742/呎
 (25年-11月-18日)</t>
         </is>
       </c>
@@ -8614,17 +8614,17 @@
       <c r="B23" s="20" t="inlineStr"/>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>A | 2269呎 (4+房)
+          <t>A | 2329呎 (4+房)
 $10428万
-$45,960/呎
+$44,776/呎
 (25年-11月-04日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>B | 2281呎 (4+房)
+          <t>B | 2335呎 (4+房)
 $11222万
-$49,198/呎
+$48,060/呎
 (25年-11月-10日)</t>
         </is>
       </c>
@@ -8641,17 +8641,17 @@
       <c r="B24" s="20" t="inlineStr"/>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>A | 2269呎 (4+房)
+          <t>A | 2329呎 (4+房)
 $10820万
-$47,686/呎
+$46,458/呎
 (25年-11月-18日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>B | 2281呎 (4+房)
+          <t>B | 2335呎 (4+房)
 $10214万
-$44,778/呎
+$43,742/呎
 (25年-11月-18日)</t>
         </is>
       </c>
@@ -8668,17 +8668,17 @@
       <c r="B25" s="20" t="inlineStr"/>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>A | 2269呎 (4+房)
+          <t>A | 2329呎 (4+房)
 $9800万
-$43,191/呎
+$42,078/呎
 (25年-11月-12日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>B | 2281呎 (4+房)
+          <t>B | 2335呎 (4+房)
 $10337万
-$45,318/呎
+$44,270/呎
 (25年-11月-12日)</t>
         </is>
       </c>
